--- a/docs/excel/Tirap_All_Depts_KPI_Collection.xlsx
+++ b/docs/excel/Tirap_All_Depts_KPI_Collection.xlsx
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Pre-Monsoon Stocking at PHCs/Schools (% complete by April)</t>
+          <t>Pre-Monsoon Stocking at PHCs/Schools (% complete)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Pre-Monsoon Stocking Complete by April</t>
+          <t>With Pre-Monsoon Stocking Complete</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
